--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1159,8 +1159,6 @@
       <c r="D38" t="n">
         <v>493.6</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>953.6</v>
       </c>
@@ -1170,7 +1168,6 @@
       <c r="I38" t="n">
         <v>194.8</v>
       </c>
-      <c r="J38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1183,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1630,6 +1627,26 @@
         <v>10.9</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEP 10, 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>456.72</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>1525.481</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-8.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1641,7 +1658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2541,6 +2558,48 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-14T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>93% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2552,7 +2611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2853,6 +2912,25 @@
       </c>
       <c r="F28" t="n">
         <v>274.66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>717</v>
+      </c>
+      <c r="C29" t="n">
+        <v>276.29</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1567</v>
+      </c>
+      <c r="F29" t="n">
+        <v>272.1</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1168,6 +1168,34 @@
       <c r="I38" t="n">
         <v>194.8</v>
       </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>502</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1026.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1683.2</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1639,7 +1667,6 @@
       <c r="C36" t="n">
         <v>5.9</v>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>1525.481</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1184,8 +1184,6 @@
       <c r="D39" t="n">
         <v>502</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>1026.7</v>
       </c>
@@ -1195,7 +1193,6 @@
       <c r="I39" t="n">
         <v>1683.2</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1208,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1674,6 +1671,26 @@
         <v>-8.9</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEP 17, 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>335.253</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-29.1</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1938.523</v>
+      </c>
+      <c r="F37" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1685,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2622,6 +2639,48 @@
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>96% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Mỹ: 13% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>57% Good to Excellent</t>
         </is>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1193,6 +1193,34 @@
       <c r="I39" t="n">
         <v>1683.2</v>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/17/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1683,7 +1711,6 @@
       <c r="C37" t="n">
         <v>-29.1</v>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>1938.523</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1209,8 +1209,6 @@
       <c r="D40" t="n">
         <v>385.1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>838.3</v>
       </c>
@@ -1220,7 +1218,6 @@
       <c r="I40" t="n">
         <v>1900</v>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1233,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1716,6 +1713,26 @@
       </c>
       <c r="F37" t="n">
         <v>24.9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SEP 24, 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>310.635</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1565.924</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-20.1</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1727,7 +1727,6 @@
       <c r="C38" t="n">
         <v>-8.6</v>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>1565.924</v>
       </c>
@@ -1746,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2725,6 +2724,51 @@
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-28T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Mỹ: 18% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>57% Good to Excellent</t>
         </is>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1218,6 +1218,34 @@
       <c r="I40" t="n">
         <v>1900</v>
       </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>536</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-36.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1445.1</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2735,7 +2763,6 @@
           <t>2026-09-28T12:00:00+0000</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2746,7 +2773,6 @@
           <t>N/A (Cuối vụ)</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2757,7 +2783,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>97% đã gieo trồng</t>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1234,8 +1234,6 @@
       <c r="D41" t="n">
         <v>315.4</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>536</v>
       </c>
@@ -1245,7 +1243,6 @@
       <c r="I41" t="n">
         <v>1445.1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1258,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1760,6 +1757,26 @@
       </c>
       <c r="F38" t="n">
         <v>-20.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OCT 01, 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>302.356</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1367.685</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-13.5</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1771,7 +1771,6 @@
       <c r="C39" t="n">
         <v>-10.3</v>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>1367.685</v>
       </c>
@@ -1790,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2813,6 +2812,51 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-05T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Mỹ: 23% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>54% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1243,6 +1243,34 @@
       <c r="I41" t="n">
         <v>1445.1</v>
       </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>451.6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>218.2</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1597.8</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2821,7 +2849,6 @@
           <t>2026-10-05T12:00:00+0000</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2832,7 +2859,6 @@
           <t>N/A (Cuối vụ)</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2843,7 +2869,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>97% đã gieo trồng</t>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1259,8 +1259,6 @@
       <c r="D42" t="n">
         <v>218.2</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>769.5</v>
       </c>
@@ -1270,7 +1268,6 @@
       <c r="I42" t="n">
         <v>1597.8</v>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2896,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3216,6 +3213,26 @@
       </c>
       <c r="F29" t="n">
         <v>272.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-09T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>740</v>
+      </c>
+      <c r="C30" t="n">
+        <v>276.04</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1849</v>
+      </c>
+      <c r="F30" t="n">
+        <v>280.44</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1280,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1803,6 +1803,26 @@
         <v>-13.5</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OCT 08, 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>304.66</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>1301.956</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-7.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1814,7 +1834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2879,6 +2899,48 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>54% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-13T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Mỹ: 33% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>56% Good to Excellent</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3289,6 @@
       <c r="C30" t="n">
         <v>276.04</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>1849</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,34 @@
       <c r="I42" t="n">
         <v>1597.8</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1815,7 +1843,6 @@
       <c r="C40" t="n">
         <v>0.7</v>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>1301.956</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1284,8 +1284,6 @@
       <c r="D43" t="n">
         <v>323.6</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>1122.4</v>
       </c>
@@ -1295,7 +1293,6 @@
       <c r="I43" t="n">
         <v>1362.6</v>
       </c>
-      <c r="J43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1308,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1850,6 +1847,26 @@
         <v>-7.2</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OCT 15, 2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>240.308</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>672.475</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-48.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1861,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2966,6 +2983,48 @@
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>56% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Mỹ: 44% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>56% Good to Excellent</t>
         </is>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1293,6 +1293,34 @@
       <c r="I43" t="n">
         <v>1362.6</v>
       </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>1527.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>780.3</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1859,7 +1887,6 @@
       <c r="C41" t="n">
         <v>-21.7</v>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>672.475</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1309,8 +1309,6 @@
       <c r="D44" t="n">
         <v>240.3</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>1527.1</v>
       </c>
@@ -1320,7 +1318,6 @@
       <c r="I44" t="n">
         <v>780.3</v>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1333,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1894,6 +1891,26 @@
         <v>-48.8</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OCT 22, 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>183.824</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>625.2329999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1905,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -3052,6 +3069,48 @@
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>56% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-26T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Mỹ: 60% thu hoạch</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>56% Good to Excellent</t>
         </is>
